--- a/udhaya.xlsx
+++ b/udhaya.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chella\eclipse-workspace\mavenCrm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23387A5-8215-4071-AF43-B4342FFEC943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175CF1B7-6C07-415F-804B-194FF72080FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="479">
   <si>
     <t>Status</t>
   </si>
@@ -1135,9 +1135,6 @@
     <t>IOB</t>
   </si>
   <si>
-    <t>Marthandam</t>
-  </si>
-  <si>
     <t>SuperAdmin</t>
   </si>
   <si>
@@ -1168,156 +1165,314 @@
     <t>weightGram</t>
   </si>
   <si>
+    <t>flexible</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>accNo</t>
+  </si>
+  <si>
+    <t>panNo</t>
+  </si>
+  <si>
+    <t>panFront</t>
+  </si>
+  <si>
+    <t>panBack</t>
+  </si>
+  <si>
+    <t>ration_02</t>
+  </si>
+  <si>
+    <t>pan_02</t>
+  </si>
+  <si>
+    <t>aadharFront</t>
+  </si>
+  <si>
+    <t>aadharBack</t>
+  </si>
+  <si>
+    <t>738920390989</t>
+  </si>
+  <si>
+    <t>XYZPC9999K</t>
+  </si>
+  <si>
+    <t>Ukkadam</t>
+  </si>
+  <si>
+    <t>Madurai west</t>
+  </si>
+  <si>
+    <t>Sowcarpet</t>
+  </si>
+  <si>
+    <t>Erode East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salem Bazaar </t>
+  </si>
+  <si>
+    <t>Dindigul Fort</t>
+  </si>
+  <si>
+    <t>Raj@1233</t>
+  </si>
+  <si>
+    <t>PanNo</t>
+  </si>
+  <si>
+    <t>VoterId</t>
+  </si>
+  <si>
+    <t>rationCard</t>
+  </si>
+  <si>
+    <t>nominieeImage</t>
+  </si>
+  <si>
+    <t>AAAPL1234C</t>
+  </si>
+  <si>
+    <t>1234 5678 9012</t>
+  </si>
+  <si>
+    <t>TN123456789012</t>
+  </si>
+  <si>
+    <t>tirupur</t>
+  </si>
+  <si>
+    <t>TimeTaken</t>
+  </si>
+  <si>
+    <t>https://staging.udhayathangamaligai.com/admin/</t>
+  </si>
+  <si>
+    <t>namakkal</t>
+  </si>
+  <si>
+    <t>P.Velur,Karur</t>
+  </si>
+  <si>
+    <t>Vengamedu</t>
+  </si>
+  <si>
+    <t>0 Pass 1 Fail</t>
+  </si>
+  <si>
+    <t>5 Pass 0 Fail</t>
+  </si>
+  <si>
+    <t>22 Sec</t>
+  </si>
+  <si>
+    <t>27 Sec</t>
+  </si>
+  <si>
+    <t>4 Pass 1 Fail</t>
+  </si>
+  <si>
+    <t>21 Sec</t>
+  </si>
+  <si>
+    <t>8 Pass 0 Fail</t>
+  </si>
+  <si>
+    <t>135 Sec</t>
+  </si>
+  <si>
+    <t>GOLD - CASH (Flexible Amount Scheme)</t>
+  </si>
+  <si>
+    <t>Gold – Cash (Fixed Amount Scheme)</t>
+  </si>
+  <si>
+    <t>Silver – Cash (Fixed Amount Scheme)</t>
+  </si>
+  <si>
+    <t>Silver-GRAM FLEXIBLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digi Gold </t>
+  </si>
+  <si>
+    <t>Digi Silver</t>
+  </si>
+  <si>
+    <t>Namakkal</t>
+  </si>
+  <si>
+    <t>Karur</t>
+  </si>
+  <si>
+    <t>P.Velur</t>
+  </si>
+  <si>
+    <t>Akshaya weight  scheme</t>
+  </si>
+  <si>
+    <t>XYZPC9999A</t>
+  </si>
+  <si>
+    <t>XYZPC9999W</t>
+  </si>
+  <si>
+    <t>XYZPC9999L</t>
+  </si>
+  <si>
+    <t>XYZPC9999M</t>
+  </si>
+  <si>
+    <t>XYZPC9999C</t>
+  </si>
+  <si>
+    <t>XYZPC9999J</t>
+  </si>
+  <si>
+    <t>738920390981</t>
+  </si>
+  <si>
+    <t>738920390982</t>
+  </si>
+  <si>
+    <t>738920390983</t>
+  </si>
+  <si>
+    <t>738920390984</t>
+  </si>
+  <si>
+    <t>738920390985</t>
+  </si>
+  <si>
+    <t>738920390986</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>amountToWeightBOW</t>
+  </si>
+  <si>
+    <t>weightBOW</t>
+  </si>
+  <si>
     <t>amountToWeightBOA</t>
   </si>
   <si>
-    <t>flexible</t>
-  </si>
-  <si>
-    <t>Digi gold</t>
-  </si>
-  <si>
-    <t>Meera Kumari</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>accNo</t>
-  </si>
-  <si>
-    <t>panNo</t>
-  </si>
-  <si>
-    <t>panFront</t>
-  </si>
-  <si>
-    <t>panBack</t>
-  </si>
-  <si>
-    <t>ration_02</t>
-  </si>
-  <si>
-    <t>pan_02</t>
-  </si>
-  <si>
-    <t>aadharFront</t>
-  </si>
-  <si>
-    <t>aadharBack</t>
-  </si>
-  <si>
-    <t>738920390989</t>
-  </si>
-  <si>
-    <t>HDFC</t>
-  </si>
-  <si>
-    <t>XYZPC9999K</t>
-  </si>
-  <si>
-    <t>Ukkadam</t>
-  </si>
-  <si>
-    <t>Madurai west</t>
-  </si>
-  <si>
-    <t>Sowcarpet</t>
-  </si>
-  <si>
-    <t>Erode East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salem Bazaar </t>
-  </si>
-  <si>
-    <t>Dindigul Fort</t>
-  </si>
-  <si>
-    <t>Raj@1233</t>
-  </si>
-  <si>
-    <t>PanNo</t>
-  </si>
-  <si>
-    <t>VoterId</t>
-  </si>
-  <si>
-    <t>rationCard</t>
-  </si>
-  <si>
-    <t>nominieeImage</t>
-  </si>
-  <si>
-    <t>AAAPL1234C</t>
-  </si>
-  <si>
-    <t>1234 5678 9012</t>
-  </si>
-  <si>
-    <t>TN123456789012</t>
-  </si>
-  <si>
-    <t>tirupur</t>
-  </si>
-  <si>
-    <t>26-DG-38</t>
-  </si>
-  <si>
-    <t>Amount To Weight Scheme</t>
-  </si>
-  <si>
-    <t>TimeTaken</t>
-  </si>
-  <si>
-    <t>https://staging.udhayathangamaligai.com/admin/</t>
-  </si>
-  <si>
-    <t>namakkal</t>
-  </si>
-  <si>
-    <t>P.Velur,Karur</t>
-  </si>
-  <si>
-    <t>Vengamedu</t>
-  </si>
-  <si>
-    <t>0 Pass 1 Fail</t>
-  </si>
-  <si>
-    <t>10 Sec</t>
-  </si>
-  <si>
-    <t>2 Pass 3 Fail</t>
-  </si>
-  <si>
-    <t>81 Sec</t>
-  </si>
-  <si>
-    <t>5 Pass 0 Fail</t>
-  </si>
-  <si>
-    <t>23 Sec</t>
-  </si>
-  <si>
-    <t>19 Sec</t>
-  </si>
-  <si>
-    <t>8 Pass 0 Fail</t>
-  </si>
-  <si>
-    <t>283 Sec</t>
-  </si>
-  <si>
-    <t>132 Sec</t>
+    <t>F-AMT-not allocated</t>
+  </si>
+  <si>
+    <t>FL-AMT-not allocated</t>
+  </si>
+  <si>
+    <t>F-AMT(S)-not allocated</t>
+  </si>
+  <si>
+    <t>FL-WT(S)-not allocated</t>
+  </si>
+  <si>
+    <t>AKS-not allocated</t>
+  </si>
+  <si>
+    <t>DG-not allocated</t>
+  </si>
+  <si>
+    <t>DS-not allocated</t>
+  </si>
+  <si>
+    <t>ration_03</t>
+  </si>
+  <si>
+    <t>pan_03</t>
+  </si>
+  <si>
+    <t>ration_04</t>
+  </si>
+  <si>
+    <t>pan_04</t>
+  </si>
+  <si>
+    <t>ration_05</t>
+  </si>
+  <si>
+    <t>pan_05</t>
+  </si>
+  <si>
+    <t>ration_06</t>
+  </si>
+  <si>
+    <t>pan_06</t>
+  </si>
+  <si>
+    <t>ration_07</t>
+  </si>
+  <si>
+    <t>pan_07</t>
+  </si>
+  <si>
+    <t>ration_08</t>
+  </si>
+  <si>
+    <t>pan_08</t>
+  </si>
+  <si>
+    <t>295 Sec</t>
+  </si>
+  <si>
+    <t>XYZPC9999G</t>
+  </si>
+  <si>
+    <t>2 Pass 2 Fail</t>
+  </si>
+  <si>
+    <t>118 Sec</t>
+  </si>
+  <si>
+    <t>FlexibleAmount</t>
+  </si>
+  <si>
+    <t>26-FL-AMT-51</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>9 Sec</t>
+  </si>
+  <si>
+    <t>26-F-AMT-52</t>
+  </si>
+  <si>
+    <t>26-F-AMT(S)-53</t>
+  </si>
+  <si>
+    <t>26-DG-54</t>
+  </si>
+  <si>
+    <t>3 Pass 0 Fail</t>
+  </si>
+  <si>
+    <t>88 Sec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="70" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1338,6 +1493,150 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -1426,36 +1725,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color indexed="17"/>
       <name val="Calibri"/>
     </font>
@@ -1483,264 +1752,6 @@
       <color indexed="17"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="17"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1763,16 +1774,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1807,38 +1817,14 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2123,124 +2109,136 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D3" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s" s="0">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>417</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="C8" t="s">
+        <v>468</v>
+      </c>
+      <c r="D8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>9</v>
+      <c r="C9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D9" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -2250,33 +2248,372 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF37BC37-2A10-492F-B32A-B95007897491}">
-  <dimension ref="A3:O3"/>
+  <dimension ref="A5:AQ13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" t="s">
+        <v>450</v>
+      </c>
+      <c r="E5" t="s">
+        <v>409</v>
+      </c>
+      <c r="F5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>10000</v>
+      </c>
+      <c r="N5">
+        <v>10000</v>
+      </c>
+      <c r="O5">
+        <v>73833</v>
+      </c>
+      <c r="P5" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>12</v>
+      </c>
+      <c r="W5" s="2">
+        <v>46170</v>
+      </c>
+      <c r="X5" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y5">
+        <v>93212</v>
+      </c>
+      <c r="Z5">
+        <v>2093005</v>
+      </c>
+      <c r="AA5">
+        <v>10000</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>444</v>
+      </c>
+      <c r="AG5">
+        <v>30000</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>458</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>459</v>
+      </c>
+      <c r="AL5" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" t="s">
+        <v>451</v>
+      </c>
+      <c r="E6" t="s">
+        <v>424</v>
+      </c>
+      <c r="F6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2000</v>
+      </c>
+      <c r="N6">
+        <v>5000</v>
+      </c>
+      <c r="O6">
+        <v>73834</v>
+      </c>
+      <c r="P6" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>12</v>
+      </c>
+      <c r="W6" s="2">
+        <v>46171</v>
+      </c>
+      <c r="X6" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y6">
+        <v>93213</v>
+      </c>
+      <c r="Z6">
+        <v>2093006</v>
+      </c>
+      <c r="AA6">
+        <v>3000</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>445</v>
+      </c>
+      <c r="AG6">
+        <v>10000</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>431</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>460</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>461</v>
+      </c>
+      <c r="AL6" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A10" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>425</v>
+      </c>
+      <c r="D10">
+        <v>8925535099</v>
+      </c>
+      <c r="E10" t="s">
+        <v>421</v>
+      </c>
+      <c r="H10" t="s">
+        <v>304</v>
+      </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" t="s">
+        <v>339</v>
+      </c>
+      <c r="O10">
+        <v>30000</v>
+      </c>
+      <c r="P10" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>384</v>
+      </c>
+      <c r="R10" t="s">
+        <v>384</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="T10" t="s">
+        <v>384</v>
+      </c>
+      <c r="U10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A11" s="40" t="s">
+        <v>379</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>425</v>
+      </c>
+      <c r="D11">
+        <v>8925535099</v>
+      </c>
+      <c r="E11" t="s">
+        <v>427</v>
+      </c>
+      <c r="H11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" t="s">
+        <v>339</v>
+      </c>
+      <c r="O11">
+        <v>10000</v>
+      </c>
+      <c r="P11" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>384</v>
+      </c>
+      <c r="R11" t="s">
+        <v>384</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="T11" t="s">
+        <v>384</v>
+      </c>
+      <c r="U11" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A12" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>381</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>382</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N3" t="s" s="0">
+      <c r="B12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" t="s">
+        <v>425</v>
+      </c>
+      <c r="D12">
+        <v>8925535099</v>
+      </c>
+      <c r="E12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" t="s">
         <v>339</v>
       </c>
-      <c r="O3" s="0">
-        <v>0</v>
+      <c r="P12" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>384</v>
+      </c>
+      <c r="R12" t="s">
+        <v>384</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="T12" t="s">
+        <v>384</v>
+      </c>
+      <c r="U12" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13">
+        <v>8925535099</v>
+      </c>
+      <c r="E13" t="s">
+        <v>423</v>
+      </c>
+      <c r="H13" t="s">
+        <v>194</v>
+      </c>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" t="s">
+        <v>339</v>
+      </c>
+      <c r="P13" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>384</v>
+      </c>
+      <c r="R13" t="s">
+        <v>384</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="T13" t="s">
+        <v>384</v>
+      </c>
+      <c r="U13" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -2289,44 +2626,44 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="2" max="2" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="62.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.90625" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
-        <v>383</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E2" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2343,120 +2680,120 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
-        <v>383</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="45" t="s">
-        <v>383</v>
-      </c>
-      <c r="B5" t="s" s="0">
+      <c r="A5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>370</v>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="46" t="s">
-        <v>383</v>
-      </c>
-      <c r="B6" t="s" s="0">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2470,120 +2807,120 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2597,117 +2934,117 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>48</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s" s="0">
+      <c r="A6" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2721,190 +3058,190 @@
   <dimension ref="A1:AR9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.6328125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="16.6328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="8.6328125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="9.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="20.90625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="22.90625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="12.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="19.90625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.08984375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="10.26953125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="7.36328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.453125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="26" max="27" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.6328125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="15.08984375"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="4.0"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="6.0"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="12.36328125"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="25.36328125"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="22.6328125"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="15.1796875"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="1" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>59</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>60</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>61</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>62</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>64</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>65</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>66</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>67</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>68</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>69</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>70</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>71</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>72</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>74</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>75</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>76</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>77</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>78</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>79</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>80</v>
       </c>
-      <c r="AH1" t="s" s="0">
+      <c r="AH1" t="s">
         <v>82</v>
       </c>
-      <c r="AI1" t="s" s="0">
+      <c r="AI1" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" t="s" s="0">
+      <c r="AJ1" t="s">
         <v>4</v>
       </c>
-      <c r="AK1" t="s" s="0">
+      <c r="AK1" t="s">
         <v>83</v>
       </c>
-      <c r="AL1" t="s" s="0">
+      <c r="AL1" t="s">
         <v>84</v>
       </c>
-      <c r="AM1" t="s" s="0">
+      <c r="AM1" t="s">
         <v>85</v>
       </c>
-      <c r="AN1" t="s" s="0">
+      <c r="AN1" t="s">
         <v>86</v>
       </c>
-      <c r="AO1" t="s" s="0">
-        <v>402</v>
-      </c>
-      <c r="AP1" t="s" s="0">
-        <v>403</v>
-      </c>
-      <c r="AQ1" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="AR1" t="s" s="0">
-        <v>405</v>
+      <c r="AO1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="28" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>87</v>
@@ -2915,38 +3252,36 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>149</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
         <v>99</v>
       </c>
@@ -2954,81 +3289,71 @@
         <v>100</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>372</v>
+        <v>203</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="X2" s="3" t="s">
         <v>103</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>154</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="Z2" s="3"/>
       <c r="AA2" s="3" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AJ2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AM2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="AN2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AP2" t="s" s="0">
-        <v>407</v>
-      </c>
-      <c r="AR2" t="s" s="0">
-        <v>388</v>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AQ2" t="s">
+        <v>403</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="29" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>87</v>
@@ -3039,36 +3364,38 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>196</v>
+        <v>91</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>197</v>
+        <v>44</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>199</v>
+        <v>94</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>201</v>
+        <v>96</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q3" s="3"/>
+        <v>97</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="R3" s="3" t="s">
         <v>99</v>
       </c>
@@ -3076,13 +3403,13 @@
         <v>100</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>203</v>
+        <v>98</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>399</v>
+        <v>98</v>
       </c>
       <c r="W3" s="3" t="s">
         <v>102</v>
@@ -3091,32 +3418,32 @@
         <v>103</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>201</v>
+        <v>96</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>209</v>
+        <v>98</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="AI3" s="3" t="s">
         <v>9</v>
@@ -3128,60 +3455,60 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
-      <c r="AQ3" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="AR3" t="s" s="0">
-        <v>388</v>
+      <c r="AO3" t="s">
+        <v>401</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="30" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>90</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>99</v>
@@ -3190,47 +3517,31 @@
         <v>100</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>104</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>401</v>
+        <v>9</v>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="AI4" s="3" t="s">
         <v>9</v>
@@ -3242,61 +3553,53 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
-      <c r="AO4" t="s" s="0">
-        <v>406</v>
-      </c>
-      <c r="AR4" t="s" s="0">
-        <v>388</v>
-      </c>
     </row>
     <row r="5" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="31" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="I5" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>118</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="Q5" s="3"/>
       <c r="R5" s="3" t="s">
         <v>99</v>
       </c>
@@ -3304,31 +3607,49 @@
         <v>100</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
+        <v>391</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="AA5" s="3" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="AH5" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="AI5" s="3" t="s">
         <v>9</v>
@@ -3342,7 +3663,7 @@
       <c r="AN5" s="3"/>
     </row>
     <row r="6" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3352,39 +3673,39 @@
         <v>87</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3" t="s">
@@ -3394,49 +3715,37 @@
         <v>100</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="X6" s="3" t="s">
         <v>133</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z6" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC6" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE6" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG6" s="3" t="s">
-        <v>131</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
       <c r="AH6" s="3" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="AI6" s="3" t="s">
         <v>9</v>
@@ -3450,51 +3759,53 @@
       <c r="AN6" s="3"/>
     </row>
     <row r="7" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="33" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>165</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q7" s="3"/>
+        <v>188</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="R7" s="3" t="s">
         <v>99</v>
       </c>
@@ -3502,23 +3813,17 @@
         <v>100</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>176</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="s">
         <v>177</v>
@@ -3532,13 +3837,13 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="AI7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="AJ7" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
@@ -3546,53 +3851,51 @@
       <c r="AN7" s="3"/>
     </row>
     <row r="8" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="34" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="I8" s="3" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
         <v>99</v>
       </c>
@@ -3600,49 +3903,75 @@
         <v>100</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+        <v>395</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="AA8" s="3" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="AH8" s="3" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="3"/>
+      <c r="AK8" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AM8" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AN8" s="3" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="9" spans="1:44" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="35" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>210</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>87</v>
@@ -3653,36 +3982,38 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>215</v>
+        <v>144</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q9" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="R9" s="3" t="s">
         <v>99</v>
       </c>
@@ -3690,25 +4021,25 @@
         <v>100</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>220</v>
+        <v>371</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>103</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>223</v>
+        <v>154</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>105</v>
@@ -3717,46 +4048,52 @@
         <v>12</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>224</v>
+        <v>155</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>225</v>
+        <v>157</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>226</v>
+        <v>158</v>
       </c>
       <c r="AI9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="AM9" s="3" t="s">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="AN9" s="3" t="s">
-        <v>230</v>
+        <v>162</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>402</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AH4" r:id="rId1" xr:uid="{939D6BFA-866E-47FE-A167-60E9B33C4530}"/>
+    <hyperlink ref="AH3" r:id="rId1" xr:uid="{939D6BFA-866E-47FE-A167-60E9B33C4530}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3767,816 +4104,816 @@
   <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="8.6328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.6328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.36328125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="5.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.08984375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="14.7265625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.26953125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="12.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="26.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.08984375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.36328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="11.08984375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="20.1796875"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="4.0"/>
-    <col min="26" max="27" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="16.08984375"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="12.7265625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="14.0"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="1" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>231</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>232</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>233</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>234</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>235</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>236</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>237</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>66</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>61</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>57</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>238</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>239</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>82</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>240</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>241</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>242</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>3</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>243</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>244</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>245</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>246</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>247</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>248</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>90</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>249</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>250</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>251</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>203</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>204</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>99</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>100</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>203</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>252</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>91</v>
       </c>
-      <c r="S2" t="s" s="0">
+      <c r="S2" t="s">
         <v>253</v>
       </c>
-      <c r="T2" t="s" s="0">
+      <c r="T2" t="s">
         <v>254</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>255</v>
       </c>
-      <c r="V2" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W2" t="s" s="0">
-        <v>414</v>
-      </c>
-      <c r="X2" t="s" s="0">
+      <c r="V2" t="s">
+        <v>368</v>
+      </c>
+      <c r="W2" t="s">
+        <v>407</v>
+      </c>
+      <c r="X2" t="s">
         <v>256</v>
       </c>
-      <c r="Y2" t="s" s="0">
+      <c r="Y2" t="s">
         <v>12</v>
       </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Z2" t="s">
         <v>257</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>212</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>258</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>259</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>40</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>260</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>261</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>164</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>165</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>262</v>
       </c>
-      <c r="G3" t="s" s="0">
+      <c r="G3" t="s">
+        <v>370</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>263</v>
+      </c>
+      <c r="R3" t="s">
+        <v>112</v>
+      </c>
+      <c r="S3" t="s">
+        <v>264</v>
+      </c>
+      <c r="T3" t="s">
+        <v>265</v>
+      </c>
+      <c r="U3" t="s">
+        <v>266</v>
+      </c>
+      <c r="V3" t="s">
+        <v>368</v>
+      </c>
+      <c r="W3" t="s">
+        <v>408</v>
+      </c>
+      <c r="X3" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A4" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K4" t="s">
+        <v>270</v>
+      </c>
+      <c r="L4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" t="s">
+        <v>100</v>
+      </c>
+      <c r="P4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>271</v>
+      </c>
+      <c r="R4" t="s">
+        <v>124</v>
+      </c>
+      <c r="S4" t="s">
+        <v>272</v>
+      </c>
+      <c r="T4" t="s">
+        <v>273</v>
+      </c>
+      <c r="U4" t="s">
+        <v>274</v>
+      </c>
+      <c r="V4" t="s">
+        <v>368</v>
+      </c>
+      <c r="W4" t="s">
+        <v>408</v>
+      </c>
+      <c r="X4" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A5" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" t="s">
+        <v>276</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O5" t="s">
+        <v>100</v>
+      </c>
+      <c r="P5" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>278</v>
+      </c>
+      <c r="R5" t="s">
+        <v>142</v>
+      </c>
+      <c r="S5" t="s">
+        <v>279</v>
+      </c>
+      <c r="T5" t="s">
+        <v>280</v>
+      </c>
+      <c r="U5" t="s">
+        <v>281</v>
+      </c>
+      <c r="V5" t="s">
+        <v>368</v>
+      </c>
+      <c r="W5" t="s">
+        <v>408</v>
+      </c>
+      <c r="X5" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>283</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>284</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>286</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
+        <v>288</v>
+      </c>
+      <c r="K6" t="s">
+        <v>289</v>
+      </c>
+      <c r="L6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M6" t="s">
+        <v>290</v>
+      </c>
+      <c r="N6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P6" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>291</v>
+      </c>
+      <c r="R6" t="s">
+        <v>166</v>
+      </c>
+      <c r="S6" t="s">
+        <v>292</v>
+      </c>
+      <c r="T6" t="s">
+        <v>293</v>
+      </c>
+      <c r="U6" t="s">
+        <v>294</v>
+      </c>
+      <c r="V6" t="s">
+        <v>368</v>
+      </c>
+      <c r="W6" t="s">
+        <v>408</v>
+      </c>
+      <c r="X6" t="s">
+        <v>295</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>297</v>
+      </c>
+      <c r="K7" t="s">
+        <v>298</v>
+      </c>
+      <c r="L7" t="s">
+        <v>150</v>
+      </c>
+      <c r="M7" t="s">
+        <v>151</v>
+      </c>
+      <c r="N7" t="s">
+        <v>99</v>
+      </c>
+      <c r="O7" t="s">
+        <v>100</v>
+      </c>
+      <c r="P7" t="s">
         <v>371</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="Q7" t="s">
+        <v>299</v>
+      </c>
+      <c r="R7" t="s">
+        <v>182</v>
+      </c>
+      <c r="S7" t="s">
+        <v>300</v>
+      </c>
+      <c r="T7" t="s">
+        <v>301</v>
+      </c>
+      <c r="U7" t="s">
+        <v>302</v>
+      </c>
+      <c r="V7" t="s">
+        <v>368</v>
+      </c>
+      <c r="W7" t="s">
+        <v>408</v>
+      </c>
+      <c r="X7" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A8" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="I8" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>117</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>119</v>
-      </c>
-      <c r="N3" t="s" s="0">
+      <c r="J8" t="s">
+        <v>307</v>
+      </c>
+      <c r="K8" t="s">
+        <v>308</v>
+      </c>
+      <c r="L8" t="s">
+        <v>190</v>
+      </c>
+      <c r="M8" t="s">
+        <v>191</v>
+      </c>
+      <c r="N8" t="s">
         <v>99</v>
       </c>
-      <c r="O3" t="s" s="0">
+      <c r="O8" t="s">
         <v>100</v>
       </c>
-      <c r="P3" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="Q3" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="R3" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="S3" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="T3" t="s" s="0">
-        <v>265</v>
-      </c>
-      <c r="U3" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="V3" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W3" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="X3" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="Y3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG3" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A4" s="67" t="s">
+      <c r="P8" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>309</v>
+      </c>
+      <c r="R8" t="s">
+        <v>196</v>
+      </c>
+      <c r="S8" t="s">
+        <v>310</v>
+      </c>
+      <c r="T8" t="s">
+        <v>311</v>
+      </c>
+      <c r="U8" t="s">
+        <v>312</v>
+      </c>
+      <c r="V8" t="s">
+        <v>368</v>
+      </c>
+      <c r="W8" t="s">
+        <v>408</v>
+      </c>
+      <c r="X8" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A9" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>140</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>268</v>
-      </c>
-      <c r="G4" t="s" s="0">
+      <c r="B9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" t="s">
+        <v>316</v>
+      </c>
+      <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s" s="0">
+      <c r="H9" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="0">
+      <c r="I9" t="s">
         <v>12</v>
       </c>
-      <c r="J4" t="s" s="0">
-        <v>269</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>270</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="N4" t="s" s="0">
+      <c r="J9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K9" t="s">
+        <v>318</v>
+      </c>
+      <c r="L9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M9" t="s">
+        <v>319</v>
+      </c>
+      <c r="N9" t="s">
         <v>99</v>
       </c>
-      <c r="O4" t="s" s="0">
+      <c r="O9" t="s">
         <v>100</v>
       </c>
-      <c r="P4" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="Q4" t="s" s="0">
-        <v>271</v>
-      </c>
-      <c r="R4" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="S4" t="s" s="0">
-        <v>272</v>
-      </c>
-      <c r="T4" t="s" s="0">
-        <v>273</v>
-      </c>
-      <c r="U4" t="s" s="0">
-        <v>274</v>
-      </c>
-      <c r="V4" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W4" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="X4" t="s" s="0">
-        <v>275</v>
-      </c>
-      <c r="Y4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG4" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A5" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>276</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s" s="0">
+      <c r="P9" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>320</v>
+      </c>
+      <c r="R9" t="s">
+        <v>213</v>
+      </c>
+      <c r="S9" t="s">
+        <v>321</v>
+      </c>
+      <c r="T9" t="s">
+        <v>322</v>
+      </c>
+      <c r="U9" t="s">
+        <v>323</v>
+      </c>
+      <c r="V9" t="s">
+        <v>368</v>
+      </c>
+      <c r="W9" t="s">
+        <v>409</v>
+      </c>
+      <c r="X9" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y9" t="s">
         <v>12</v>
       </c>
-      <c r="J5" t="s" s="0">
-        <v>277</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="M5" t="s" s="0">
-        <v>132</v>
-      </c>
-      <c r="N5" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="O5" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="P5" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="Q5" t="s" s="0">
-        <v>278</v>
-      </c>
-      <c r="R5" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="S5" t="s" s="0">
-        <v>279</v>
-      </c>
-      <c r="T5" t="s" s="0">
-        <v>280</v>
-      </c>
-      <c r="U5" t="s" s="0">
-        <v>281</v>
-      </c>
-      <c r="V5" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W5" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="X5" t="s" s="0">
-        <v>282</v>
-      </c>
-      <c r="Y5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="s" s="0">
-        <v>283</v>
-      </c>
-      <c r="AA5" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="AB5" t="s" s="0">
-        <v>284</v>
-      </c>
-      <c r="AC5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="AE5" t="s" s="0">
-        <v>285</v>
-      </c>
-      <c r="AF5" t="s" s="0">
-        <v>286</v>
-      </c>
-      <c r="AG5" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A6" s="69" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>194</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>195</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>287</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>288</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>289</v>
-      </c>
-      <c r="L6" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="M6" t="s" s="0">
-        <v>290</v>
-      </c>
-      <c r="N6" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="O6" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="P6" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="Q6" t="s" s="0">
-        <v>291</v>
-      </c>
-      <c r="R6" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="S6" t="s" s="0">
-        <v>292</v>
-      </c>
-      <c r="T6" t="s" s="0">
-        <v>293</v>
-      </c>
-      <c r="U6" t="s" s="0">
-        <v>294</v>
-      </c>
-      <c r="V6" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W6" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="X6" t="s" s="0">
-        <v>295</v>
-      </c>
-      <c r="Y6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A7" s="70" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>179</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>296</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="I7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>297</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>298</v>
-      </c>
-      <c r="L7" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="M7" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="N7" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="O7" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="P7" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="Q7" t="s" s="0">
-        <v>299</v>
-      </c>
-      <c r="R7" t="s" s="0">
-        <v>182</v>
-      </c>
-      <c r="S7" t="s" s="0">
-        <v>300</v>
-      </c>
-      <c r="T7" t="s" s="0">
-        <v>301</v>
-      </c>
-      <c r="U7" t="s" s="0">
-        <v>302</v>
-      </c>
-      <c r="V7" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W7" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="X7" t="s" s="0">
-        <v>303</v>
-      </c>
-      <c r="Y7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG7" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A8" s="71" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>193</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>304</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>305</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>306</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="I8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>307</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>308</v>
-      </c>
-      <c r="L8" t="s" s="0">
-        <v>190</v>
-      </c>
-      <c r="M8" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="N8" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="O8" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="P8" t="s" s="0">
-        <v>190</v>
-      </c>
-      <c r="Q8" t="s" s="0">
-        <v>309</v>
-      </c>
-      <c r="R8" t="s" s="0">
-        <v>196</v>
-      </c>
-      <c r="S8" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="T8" t="s" s="0">
-        <v>311</v>
-      </c>
-      <c r="U8" t="s" s="0">
-        <v>312</v>
-      </c>
-      <c r="V8" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W8" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="X8" t="s" s="0">
-        <v>313</v>
-      </c>
-      <c r="Y8" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG8" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A9" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>314</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>315</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="G9" t="s" s="0">
+      <c r="Z9" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD9" t="s">
         <v>39</v>
       </c>
-      <c r="H9" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="J9" t="s" s="0">
-        <v>317</v>
-      </c>
-      <c r="K9" t="s" s="0">
-        <v>318</v>
-      </c>
-      <c r="L9" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="M9" t="s" s="0">
-        <v>319</v>
-      </c>
-      <c r="N9" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="O9" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="P9" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="Q9" t="s" s="0">
-        <v>320</v>
-      </c>
-      <c r="R9" t="s" s="0">
-        <v>213</v>
-      </c>
-      <c r="S9" t="s" s="0">
-        <v>321</v>
-      </c>
-      <c r="T9" t="s" s="0">
-        <v>322</v>
-      </c>
-      <c r="U9" t="s" s="0">
-        <v>323</v>
-      </c>
-      <c r="V9" t="s" s="0">
-        <v>369</v>
-      </c>
-      <c r="W9" t="s" s="0">
-        <v>416</v>
-      </c>
-      <c r="X9" t="s" s="0">
-        <v>324</v>
-      </c>
-      <c r="Y9" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="Z9" t="s" s="0">
-        <v>325</v>
-      </c>
-      <c r="AA9" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="AB9" t="s" s="0">
-        <v>326</v>
-      </c>
-      <c r="AC9" t="s" s="0">
-        <v>327</v>
-      </c>
-      <c r="AD9" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="AE9" t="s" s="0">
+      <c r="AE9" t="s">
         <v>328</v>
       </c>
-      <c r="AF9" t="s" s="0">
+      <c r="AF9" t="s">
         <v>329</v>
       </c>
-      <c r="AG9" t="s" s="0">
+      <c r="AG9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4587,141 +4924,219 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.90625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="11.36328125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="3.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="8.36328125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="7.36328125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="12.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="1" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>241</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>330</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>331</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>332</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>333</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>334</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>335</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>336</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>337</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>338</v>
       </c>
-      <c r="O1" t="s" s="0">
-        <v>377</v>
-      </c>
-      <c r="P1" t="s" s="0">
+      <c r="O1" t="s">
+        <v>376</v>
+      </c>
+      <c r="P1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>382</v>
+      </c>
+      <c r="R1" t="s">
+        <v>383</v>
+      </c>
+      <c r="S1" t="s">
+        <v>81</v>
+      </c>
+      <c r="T1" t="s">
+        <v>386</v>
+      </c>
+      <c r="U1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D2">
+        <v>8925535099</v>
+      </c>
+      <c r="E2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" t="s">
+        <v>339</v>
+      </c>
+      <c r="P2" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>384</v>
+      </c>
+      <c r="R2" t="s">
         <v>385</v>
       </c>
-      <c r="Q1" t="s" s="0">
-        <v>386</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="S1" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="U1" t="s" s="0">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="S2" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="T2" t="s">
+        <v>384</v>
+      </c>
+      <c r="U2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="D2" s="0">
-        <v>9965331986</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>411</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N2" t="s" s="0">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D3">
+        <v>8925535099</v>
+      </c>
+      <c r="E3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" t="s">
         <v>339</v>
       </c>
-      <c r="O2" s="0">
-        <v>1000</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>394</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="R2" t="s" s="0">
-        <v>389</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="T2" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="U2" t="s" s="0">
-        <v>388</v>
+      <c r="O3">
+        <v>20000</v>
+      </c>
+      <c r="P3" t="s">
+        <v>428</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="T3" t="s">
+        <v>384</v>
+      </c>
+      <c r="U3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D4">
+        <v>8925535099</v>
+      </c>
+      <c r="E4" t="s">
+        <v>420</v>
+      </c>
+      <c r="H4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" t="s">
+        <v>339</v>
+      </c>
+      <c r="O4">
+        <v>10000</v>
+      </c>
+      <c r="P4" t="s">
+        <v>429</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="T4" t="s">
+        <v>384</v>
+      </c>
+      <c r="U4" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4733,285 +5148,650 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="6.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="14.54296875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.26953125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="7.54296875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.08984375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="9.36328125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="6.7265625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="6.81640625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.08984375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="10.36328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.81640625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.54296875"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="10.36328125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="7.54296875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="31" max="31" customWidth="true" width="12.1796875"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.81640625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="11.6328125"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="12.90625"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>340</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>341</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>241</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>342</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>343</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>344</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>345</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>350</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>351</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>352</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>353</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>354</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>355</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>356</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>357</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>358</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>359</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>360</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>361</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>362</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC1" t="s">
         <v>373</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>374</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AE1" t="s">
+        <v>377</v>
+      </c>
+      <c r="AF1" t="s">
         <v>375</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>378</v>
       </c>
-      <c r="AF1" t="s" s="0">
-        <v>376</v>
-      </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AH1" t="s">
         <v>380</v>
       </c>
-      <c r="AH1" t="s" s="0">
+      <c r="AI1" t="s">
+        <v>381</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>382</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>383</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>386</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A2" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2">
+        <v>8925535099</v>
+      </c>
+      <c r="D2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>10000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M2">
+        <v>20310</v>
+      </c>
+      <c r="N2">
+        <v>7000</v>
+      </c>
+      <c r="O2">
+        <v>73831</v>
+      </c>
+      <c r="P2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" s="2">
+        <v>46168</v>
+      </c>
+      <c r="X2" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y2">
+        <v>93211</v>
+      </c>
+      <c r="Z2">
+        <v>2093003</v>
+      </c>
+      <c r="AA2">
+        <v>3000</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>470</v>
+      </c>
+      <c r="AG2">
+        <v>20000</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>474</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>428</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>454</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>455</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="AM2" t="s">
         <v>384</v>
       </c>
-      <c r="AI1" t="s" s="0">
+      <c r="AN2" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A3" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3">
+        <v>8925535099</v>
+      </c>
+      <c r="D3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E3" t="s">
+        <v>426</v>
+      </c>
+      <c r="F3" t="s">
+        <v>472</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>364</v>
+      </c>
+      <c r="K3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M3">
+        <v>20311</v>
+      </c>
+      <c r="N3">
+        <v>8000</v>
+      </c>
+      <c r="O3">
+        <v>73832</v>
+      </c>
+      <c r="P3" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="2"/>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W3" s="2">
+        <v>46169</v>
+      </c>
+      <c r="X3" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y3">
+        <v>93211</v>
+      </c>
+      <c r="Z3">
+        <v>2093004</v>
+      </c>
+      <c r="AA3">
+        <v>2000</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>470</v>
+      </c>
+      <c r="AG3">
+        <v>10000</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>475</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>456</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>457</v>
+      </c>
+      <c r="AL3" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A4" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4">
+        <v>8925535099</v>
+      </c>
+      <c r="D4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F4" t="s">
+        <v>472</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>3000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>446</v>
+      </c>
+      <c r="AG4">
+        <v>3000</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>476</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>432</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>462</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>463</v>
+      </c>
+      <c r="AL4" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A5" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C5">
+        <v>8925535099</v>
+      </c>
+      <c r="D5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F5" t="s">
+        <v>472</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K5" t="s">
+        <v>365</v>
+      </c>
+      <c r="M5">
+        <v>20319</v>
+      </c>
+      <c r="N5">
+        <v>600</v>
+      </c>
+      <c r="O5">
+        <v>73830</v>
+      </c>
+      <c r="P5" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>366</v>
+      </c>
+      <c r="R5" t="s">
+        <v>367</v>
+      </c>
+      <c r="S5" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T5">
+        <v>39480</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>12</v>
+      </c>
+      <c r="W5" s="2">
+        <v>46167</v>
+      </c>
+      <c r="X5" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y5">
+        <v>93209</v>
+      </c>
+      <c r="Z5">
+        <v>2093002</v>
+      </c>
+      <c r="AA5">
+        <v>300</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5">
+        <v>124356</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>470</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>471</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>389</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>384</v>
+      </c>
+      <c r="AK5" t="s">
         <v>385</v>
       </c>
-      <c r="AJ1" t="s" s="0">
-        <v>386</v>
-      </c>
-      <c r="AK1" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="AL1" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="AM1" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="AN1" t="s" s="0">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="C2" s="0">
-        <v>9965331986</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>410</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>248</v>
-      </c>
-      <c r="G2" s="0">
-        <v>1000</v>
-      </c>
-      <c r="H2" s="0">
-        <v>100</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>365</v>
-      </c>
-      <c r="M2" s="0">
-        <v>20309</v>
-      </c>
-      <c r="N2" s="0">
-        <v>600</v>
-      </c>
-      <c r="O2" s="0">
-        <v>73830</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="R2" t="s" s="0">
-        <v>367</v>
-      </c>
-      <c r="S2" s="2">
-        <v>46146</v>
-      </c>
-      <c r="T2" s="0">
-        <v>39480</v>
-      </c>
-      <c r="V2" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="W2" s="2">
-        <v>46167</v>
-      </c>
-      <c r="X2" t="s" s="0">
-        <v>393</v>
-      </c>
-      <c r="Y2" s="0">
-        <v>93209</v>
-      </c>
-      <c r="Z2" s="0">
-        <v>2093002</v>
-      </c>
-      <c r="AA2" s="0">
-        <v>300</v>
-      </c>
-      <c r="AB2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="0">
-        <v>124356</v>
-      </c>
-      <c r="AD2" s="0">
+      <c r="AL5" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="P6" t="s">
+        <v>9</v>
+      </c>
+      <c r="U6">
         <v>0</v>
       </c>
-      <c r="AF2" t="s" s="0">
-        <v>379</v>
-      </c>
-      <c r="AG2" s="0">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="s" s="0">
-        <v>410</v>
-      </c>
-      <c r="AI2" t="s" s="0">
-        <v>394</v>
-      </c>
-      <c r="AJ2" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="AK2" t="s" s="0">
-        <v>389</v>
-      </c>
-      <c r="AL2" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="AM2" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="AN2" t="s" s="0">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="R5" s="5"/>
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>446</v>
+      </c>
+      <c r="AG6">
+        <v>5000</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>433</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>464</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>465</v>
+      </c>
+      <c r="AL6" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>423</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
